--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/demitas.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/demitas.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="demitas" sheetId="1" r:id="rId3"/>
+    <sheet name="demitas" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="R1C1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="R1C1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -199,37 +199,6 @@
   <si>
     <t xml:space="preserve">end</t>
   </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">诸神与古老的存在实在傲慢。他们活得太久，已然扭曲了世界的法则。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我有想问的事情</t>
-  </si>
-  <si>
-    <t xml:space="preserve">想要吾的知识吗。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">关于魔法书预约</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(返回)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嚯…汝对魔法有兴趣？
-若有想要复制的魔法书，尽可托付于吾。将卢恩文字逐字逐句解读并作成抄本实乃艰辛之事。若有兴致，吾可为汝将其复制。
-有些书籍会较为难以解读，但若时间充裕依可复制。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">……#pc。吾有话对汝说。
-曾经身为人类时，吾深入研究过卢恩文字，并掌握书写古老魔法书的技艺。此技在世间早已无人知晓，实为稀有之技。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">自吾留于此地以来，本欲远远守望汝等，但汝若与伊斯西泽尔对峙，必然需要吾的知识。
-……若汝渴望魔法的助力，可到此处找吾。</t>
-  </si>
 </sst>
 </file>
 
@@ -249,25 +218,25 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -300,7 +269,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -309,66 +278,66 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -382,13 +351,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -564,26 +533,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M32"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.85" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
-    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
-    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
-    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
-    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.06"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -621,24 +590,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="I2" s="1">
-        <f>MAX(I4:I1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="1" t="n">
+        <f aca="false">MAX(I4:I1048576)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="23.85">
-      <c r="I8" s="1">
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -647,15 +616,12 @@
       <c r="K8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="L8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" ht="12.8">
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" ht="12.8">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
@@ -665,7 +631,7 @@
       <c r="E10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -674,11 +640,8 @@
       <c r="K10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" ht="12.8">
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E11" s="1" t="s">
         <v>21</v>
       </c>
@@ -686,17 +649,17 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" ht="12.8">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" ht="12.8">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E13" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" ht="12.8">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
         <v>16</v>
       </c>
@@ -707,7 +670,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
-      <c r="I15" s="1">
+      <c r="I15" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J15" s="6" t="s">
@@ -716,12 +679,10 @@
       <c r="K15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="L15" s="6" t="s">
-        <v>47</v>
-      </c>
+      <c r="L15" s="6"/>
       <c r="M15" s="1"/>
     </row>
-    <row r="16" ht="12.8">
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6"/>
       <c r="B16" s="6" t="s">
         <v>27</v>
@@ -734,7 +695,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
-      <c r="I16" s="1">
+      <c r="I16" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J16" s="6" t="s">
@@ -743,12 +704,10 @@
       <c r="K16" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="L16" s="6" t="s">
-        <v>48</v>
-      </c>
+      <c r="L16" s="6"/>
       <c r="M16" s="1"/>
     </row>
-    <row r="17" ht="12.8">
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
       <c r="B17" s="6" t="s">
         <v>13</v>
@@ -761,7 +720,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
-      <c r="I17" s="1">
+      <c r="I17" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J17" s="6" t="s">
@@ -770,12 +729,10 @@
       <c r="K17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="L17" s="6" t="s">
-        <v>49</v>
-      </c>
+      <c r="L17" s="6"/>
       <c r="M17" s="1"/>
     </row>
-    <row r="18" ht="12.8">
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6"/>
       <c r="B18" s="6" t="s">
         <v>13</v>
@@ -793,7 +750,7 @@
       <c r="L18" s="6"/>
       <c r="M18" s="1"/>
     </row>
-    <row r="19" ht="12.8">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -807,7 +764,7 @@
       <c r="L19" s="6"/>
       <c r="M19" s="1"/>
     </row>
-    <row r="20" ht="12.8">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -821,7 +778,7 @@
       <c r="L20" s="6"/>
       <c r="M20" s="1"/>
     </row>
-    <row r="21" ht="22.35">
+    <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
         <v>27</v>
       </c>
@@ -837,7 +794,7 @@
       <c r="L21" s="6"/>
       <c r="M21" s="1"/>
     </row>
-    <row r="22" ht="105.95">
+    <row r="22" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -846,7 +803,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
-      <c r="I22" s="1">
+      <c r="I22" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J22" s="3" t="s">
@@ -855,12 +812,10 @@
       <c r="K22" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="L22" s="6" t="s">
-        <v>50</v>
-      </c>
+      <c r="L22" s="6"/>
       <c r="M22" s="1"/>
     </row>
-    <row r="23" ht="12.8">
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6"/>
       <c r="B23" s="6" t="s">
         <v>34</v>
@@ -876,12 +831,12 @@
       <c r="L23" s="6"/>
       <c r="M23" s="1"/>
     </row>
-    <row r="27" ht="12.8">
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" ht="12.8">
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E28" s="1" t="s">
         <v>36</v>
       </c>
@@ -889,8 +844,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="29" ht="56.7">
-      <c r="I29" s="1">
+    <row r="29" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I29" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J29" s="3" t="s">
@@ -899,12 +854,9 @@
       <c r="K29" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="L29" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" ht="57.45">
-      <c r="I30" s="1">
+    </row>
+    <row r="30" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I30" s="1" t="n">
         <v>8</v>
       </c>
       <c r="J30" s="3" t="s">
@@ -913,28 +865,25 @@
       <c r="K30" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L30" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" ht="12.8">
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E31" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="32" ht="12.8">
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E32" s="1" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/demitas.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/demitas.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="demitas" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="demitas" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="R1C1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="R1C1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="53">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -199,6 +199,37 @@
   <si>
     <t xml:space="preserve">end</t>
   </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">诸神与古老的存在实在傲慢。他们活得太久，已然扭曲了世界的法则。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我有想问的事情</t>
+  </si>
+  <si>
+    <t xml:space="preserve">想要吾的知识吗。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">关于魔法书预约</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(返回)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嚯…汝对魔法有兴趣？
+若有想要复制的魔法书，尽可托付于吾。将卢恩文字逐字逐句解读并作成抄本实乃艰辛之事。若有兴致，吾可为汝将其复制。
+有些书籍会较为难以解读，但若时间充裕依可复制。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">……#pc。吾有话对汝说。
+曾经身为人类时，吾深入研究过卢恩文字，并掌握书写古老魔法书的技艺。此技在世间早已无人知晓，实为稀有之技。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自吾留于此地以来，本欲远远守望汝等，但汝若与伊斯西泽尔对峙，必然需要吾的知识。
+……若汝渴望魔法的助力，可到此处找吾。</t>
+  </si>
 </sst>
 </file>
 
@@ -218,25 +249,25 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -269,7 +300,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -278,66 +309,66 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -351,13 +382,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -533,26 +564,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M32"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.06"/>
+    <col min="1" max="1" width="8.85" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
+    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
+    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
+    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
+    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -590,24 +621,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I2" s="1" t="n">
-        <f aca="false">MAX(I4:I1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="I2" s="1">
+        <f>MAX(I4:I1048576)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I8" s="1" t="n">
+    <row r="8" ht="23.85">
+      <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -616,12 +647,15 @@
       <c r="K8" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" ht="12.8">
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.8">
       <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
@@ -631,7 +665,7 @@
       <c r="E10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="1" t="n">
+      <c r="I10" s="1">
         <v>2</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -640,8 +674,11 @@
       <c r="K10" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" ht="12.8">
       <c r="E11" s="1" t="s">
         <v>21</v>
       </c>
@@ -649,17 +686,17 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.8">
       <c r="E12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="12.8">
       <c r="E13" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="12.8">
       <c r="A15" s="6" t="s">
         <v>16</v>
       </c>
@@ -670,7 +707,7 @@
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
-      <c r="I15" s="1" t="n">
+      <c r="I15" s="1">
         <v>3</v>
       </c>
       <c r="J15" s="6" t="s">
@@ -679,10 +716,12 @@
       <c r="K15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="L15" s="6"/>
+      <c r="L15" s="6" t="s">
+        <v>47</v>
+      </c>
       <c r="M15" s="1"/>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="12.8">
       <c r="A16" s="6"/>
       <c r="B16" s="6" t="s">
         <v>27</v>
@@ -695,7 +734,7 @@
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
-      <c r="I16" s="1" t="n">
+      <c r="I16" s="1">
         <v>4</v>
       </c>
       <c r="J16" s="6" t="s">
@@ -704,10 +743,12 @@
       <c r="K16" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="L16" s="6"/>
+      <c r="L16" s="6" t="s">
+        <v>48</v>
+      </c>
       <c r="M16" s="1"/>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" ht="12.8">
       <c r="A17" s="6"/>
       <c r="B17" s="6" t="s">
         <v>13</v>
@@ -720,7 +761,7 @@
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
-      <c r="I17" s="1" t="n">
+      <c r="I17" s="1">
         <v>5</v>
       </c>
       <c r="J17" s="6" t="s">
@@ -729,10 +770,12 @@
       <c r="K17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="L17" s="6"/>
+      <c r="L17" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="M17" s="1"/>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" ht="12.8">
       <c r="A18" s="6"/>
       <c r="B18" s="6" t="s">
         <v>13</v>
@@ -750,7 +793,7 @@
       <c r="L18" s="6"/>
       <c r="M18" s="1"/>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" ht="12.8">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -764,7 +807,7 @@
       <c r="L19" s="6"/>
       <c r="M19" s="1"/>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="12.8">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -778,7 +821,7 @@
       <c r="L20" s="6"/>
       <c r="M20" s="1"/>
     </row>
-    <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="22.35">
       <c r="A21" s="6" t="s">
         <v>27</v>
       </c>
@@ -794,7 +837,7 @@
       <c r="L21" s="6"/>
       <c r="M21" s="1"/>
     </row>
-    <row r="22" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" ht="105.95">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -803,7 +846,7 @@
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
-      <c r="I22" s="1" t="n">
+      <c r="I22" s="1">
         <v>6</v>
       </c>
       <c r="J22" s="3" t="s">
@@ -812,10 +855,12 @@
       <c r="K22" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="L22" s="6"/>
+      <c r="L22" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="M22" s="1"/>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" ht="12.8">
       <c r="A23" s="6"/>
       <c r="B23" s="6" t="s">
         <v>34</v>
@@ -831,12 +876,12 @@
       <c r="L23" s="6"/>
       <c r="M23" s="1"/>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="12.8">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" ht="12.8">
       <c r="E28" s="1" t="s">
         <v>36</v>
       </c>
@@ -844,8 +889,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I29" s="1" t="n">
+    <row r="29" ht="56.7">
+      <c r="I29" s="1">
         <v>7</v>
       </c>
       <c r="J29" s="3" t="s">
@@ -854,9 +899,12 @@
       <c r="K29" s="7" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I30" s="1" t="n">
+      <c r="L29" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" ht="57.45">
+      <c r="I30" s="1">
         <v>8</v>
       </c>
       <c r="J30" s="3" t="s">
@@ -865,25 +913,28 @@
       <c r="K30" s="7" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L30" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" ht="12.8">
       <c r="E31" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" ht="12.8">
       <c r="E32" s="1" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
